--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
@@ -935,94 +935,94 @@
     <t>214</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>R$ 4.002,84</t>
-  </si>
-  <si>
-    <t>44.3</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>4.68</t>
-  </si>
-  <si>
-    <t>18.3</t>
-  </si>
-  <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>5.1</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 4.033,71</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>4.74</t>
+  </si>
+  <si>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>6.1</t>
   </si>
   <si>
     <t>44.3%</t>
   </si>
   <si>
-    <t>17.9%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
+    <t>19.0%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.3%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>7.0%</t>
+    <t>7.1%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>979.0</t>
-  </si>
-  <si>
-    <t>759.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>223.0</t>
-  </si>
-  <si>
-    <t>70.0</t>
-  </si>
-  <si>
-    <t>14.0</t>
-  </si>
-  <si>
-    <t>298.0</t>
-  </si>
-  <si>
-    <t>116.0</t>
-  </si>
-  <si>
-    <t>130.0</t>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>1244.0</t>
+  </si>
+  <si>
+    <t>974.0</t>
+  </si>
+  <si>
+    <t>120.0</t>
+  </si>
+  <si>
+    <t>12.0</t>
+  </si>
+  <si>
+    <t>277.0</t>
+  </si>
+  <si>
+    <t>83.0</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>366.0</t>
+  </si>
+  <si>
+    <t>140.0</t>
+  </si>
+  <si>
+    <t>205.0</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>28.0</t>
+    <t>37.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>7463.54</v>
+      </c>
+      <c r="N6" s="6">
+        <v>83</v>
+      </c>
+      <c r="O6" s="6">
+        <v>67</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.9392405063291136</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>14.949999999999999</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.1146469696969699</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.52238805970149249</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.059701492537313432</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -3242,7 +3300,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3272,35 +3330,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>5787.3400000000001</v>
+      </c>
+      <c r="N13" s="6">
+        <v>70</v>
+      </c>
+      <c r="O13" s="6">
+        <v>53</v>
+      </c>
+      <c r="P13" s="7">
+        <v>6.9811899999999998</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>20.055975471698112</v>
+      </c>
+      <c r="R13" s="8">
+        <v>5.5955981132075481</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.30188679245283018</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.20754716981132076</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.11320754716981132</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -3494,7 +3610,7 @@
         <v>19519</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>51</v>
@@ -3524,35 +3640,93 @@
         <v>58</v>
       </c>
       <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="6"/>
-      <c r="AL15" s="6"/>
-      <c r="AM15" s="6"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="6"/>
+      <c r="M15" s="5">
+        <v>10459.059999999999</v>
+      </c>
+      <c r="N15" s="6">
+        <v>116</v>
+      </c>
+      <c r="O15" s="6">
+        <v>74</v>
+      </c>
+      <c r="P15" s="7">
+        <v>4.6126050420168063</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>15.62680135135135</v>
+      </c>
+      <c r="R15" s="8">
+        <v>3.4417808219178081</v>
+      </c>
+      <c r="S15" s="8">
+        <v>7</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0.67567567567567566</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0.13513513513513514</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0.027027027027027029</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0.027027027027027029</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0.054054054054054057</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0.054054054054054057</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="6">
+        <v>2</v>
+      </c>
+      <c r="AK15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP15" s="4">
         <v>58</v>
       </c>
@@ -5415,7 +5589,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5445,35 +5619,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>5316.2200000000003</v>
+      </c>
+      <c r="N28" s="6">
+        <v>68</v>
+      </c>
+      <c r="O28" s="6">
+        <v>24</v>
+      </c>
+      <c r="P28" s="7">
+        <v>6.6037878787878794</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="R28" s="8">
+        <v>8.5590291666666669</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -5828,7 +6060,7 @@
         <v>19551</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>51</v>
@@ -5858,35 +6090,93 @@
         <v>58</v>
       </c>
       <c r="L31" s="4"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-      <c r="AB31" s="9"/>
-      <c r="AC31" s="9"/>
-      <c r="AD31" s="6"/>
-      <c r="AE31" s="6"/>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="6"/>
-      <c r="AI31" s="6"/>
-      <c r="AJ31" s="6"/>
-      <c r="AK31" s="6"/>
-      <c r="AL31" s="6"/>
-      <c r="AM31" s="6"/>
-      <c r="AN31" s="9"/>
-      <c r="AO31" s="6"/>
+      <c r="M31" s="5">
+        <v>7184.46</v>
+      </c>
+      <c r="N31" s="6">
+        <v>61</v>
+      </c>
+      <c r="O31" s="6">
+        <v>39</v>
+      </c>
+      <c r="P31" s="7">
+        <v>5.6262295081967215</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>19.850428205128203</v>
+      </c>
+      <c r="R31" s="8">
+        <v>5.7763157894736841</v>
+      </c>
+      <c r="S31" s="8">
+        <v>8</v>
+      </c>
+      <c r="T31" s="9">
+        <v>0.25641025641025639</v>
+      </c>
+      <c r="U31" s="9">
+        <v>0.28205128205128205</v>
+      </c>
+      <c r="V31" s="9">
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="W31" s="9">
+        <v>0</v>
+      </c>
+      <c r="X31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AB31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE31" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF31" s="6">
+        <v>7</v>
+      </c>
+      <c r="AG31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="9">
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="AO31" s="6">
+        <v>7</v>
+      </c>
       <c t="s" r="AP31" s="4">
         <v>58</v>
       </c>
@@ -6495,7 +6785,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6525,35 +6815,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>5093.0299999999997</v>
+      </c>
+      <c r="N36" s="6">
+        <v>44</v>
+      </c>
+      <c r="O36" s="6">
+        <v>31</v>
+      </c>
+      <c r="P36" s="7">
+        <v>7.4297619047619055</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>20.723889999999997</v>
+      </c>
+      <c r="R36" s="8">
+        <v>6.1235620689655175</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0.032258064516000003</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -6906,7 +7254,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6936,35 +7284,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>4907.1300000000001</v>
+      </c>
+      <c r="N39" s="6">
+        <v>59</v>
+      </c>
+      <c r="O39" s="6">
+        <v>39</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.4882189655172415</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>14.012392307692307</v>
+      </c>
+      <c r="R39" s="8">
+        <v>5.9183896551724136</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7319,7 +7725,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7349,35 +7755,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>3332.5999999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>42</v>
+      </c>
+      <c r="O42" s="6">
+        <v>30</v>
+      </c>
+      <c r="P42" s="7">
+        <v>4.5865853658536588</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>17.765000000000001</v>
+      </c>
+      <c r="R42" s="8">
+        <v>5.7261100000000003</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -7889,7 +8353,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -7917,35 +8381,93 @@
         <v>58</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="9"/>
-      <c r="AC46" s="9"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="9"/>
-      <c r="AO46" s="6"/>
+      <c r="M46" s="5">
+        <v>3419.98</v>
+      </c>
+      <c r="N46" s="6">
+        <v>52</v>
+      </c>
+      <c r="O46" s="6">
+        <v>29</v>
+      </c>
+      <c r="P46" s="7">
+        <v>2.2153846153846155</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>15.614941379310345</v>
+      </c>
+      <c r="R46" s="8">
+        <v>6.8398821428571424</v>
+      </c>
+      <c r="S46" s="8">
+        <v>7</v>
+      </c>
+      <c r="T46" s="9">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="U46" s="9">
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="V46" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="W46" s="9">
+        <v>0</v>
+      </c>
+      <c r="X46" s="9">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="Y46" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AB46" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AC46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP46" s="4">
         <v>58</v>
       </c>
@@ -8453,7 +8975,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8483,35 +9005,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>5586.29</v>
+      </c>
+      <c r="N50" s="6">
+        <v>54</v>
+      </c>
+      <c r="O50" s="6">
+        <v>28</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.1245098039215686</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>15.189285714285715</v>
+      </c>
+      <c r="R50" s="8">
+        <v>5.0619035714285721</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8808,7 +9388,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>51</v>
@@ -8836,35 +9416,93 @@
         <v>58</v>
       </c>
       <c r="L53" s="4"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="8"/>
-      <c r="S53" s="8"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="M53" s="5">
+        <v>2998.3499999999999</v>
+      </c>
+      <c r="N53" s="6">
+        <v>40</v>
+      </c>
+      <c r="O53" s="6">
+        <v>29</v>
+      </c>
+      <c r="P53" s="7">
+        <v>3.2825195121951221</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>14.074713793103449</v>
+      </c>
+      <c r="R53" s="8">
+        <v>3.7172413793103449</v>
+      </c>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
+      <c r="T53" s="9">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -12008,7 +12646,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -12038,35 +12676,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>3496.6300000000001</v>
+      </c>
+      <c r="N75" s="6">
+        <v>41</v>
+      </c>
+      <c r="O75" s="6">
+        <v>26</v>
+      </c>
+      <c r="P75" s="7">
+        <v>4.1317837209302324</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>18.73141153846154</v>
+      </c>
+      <c r="R75" s="8">
+        <v>8.1366680000000002</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -12359,7 +13055,7 @@
         <v>19666</v>
       </c>
       <c r="B78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C78" s="4">
         <v>51</v>
@@ -12387,35 +13083,93 @@
         <v>58</v>
       </c>
       <c r="L78" s="4"/>
-      <c r="M78" s="5"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="8"/>
-      <c r="R78" s="8"/>
-      <c r="S78" s="8"/>
-      <c r="T78" s="9"/>
-      <c r="U78" s="9"/>
-      <c r="V78" s="9"/>
-      <c r="W78" s="9"/>
-      <c r="X78" s="9"/>
-      <c r="Y78" s="9"/>
-      <c r="Z78" s="9"/>
-      <c r="AA78" s="9"/>
-      <c r="AB78" s="9"/>
-      <c r="AC78" s="9"/>
-      <c r="AD78" s="6"/>
-      <c r="AE78" s="6"/>
-      <c r="AF78" s="6"/>
-      <c r="AG78" s="6"/>
-      <c r="AH78" s="6"/>
-      <c r="AI78" s="6"/>
-      <c r="AJ78" s="6"/>
-      <c r="AK78" s="6"/>
-      <c r="AL78" s="6"/>
-      <c r="AM78" s="6"/>
-      <c r="AN78" s="9"/>
-      <c r="AO78" s="6"/>
+      <c r="M78" s="5">
+        <v>5074.3800000000001</v>
+      </c>
+      <c r="N78" s="6">
+        <v>49</v>
+      </c>
+      <c r="O78" s="6">
+        <v>41</v>
+      </c>
+      <c r="P78" s="7">
+        <v>4.8938775510204087</v>
+      </c>
+      <c r="Q78" s="8">
+        <v>15.998373170731709</v>
+      </c>
+      <c r="R78" s="8">
+        <v>3.5764948717948721</v>
+      </c>
+      <c r="S78" s="8">
+        <v>8</v>
+      </c>
+      <c r="T78" s="9">
+        <v>0.43902439024390244</v>
+      </c>
+      <c r="U78" s="9">
+        <v>0.12195121951219512</v>
+      </c>
+      <c r="V78" s="9">
+        <v>0</v>
+      </c>
+      <c r="W78" s="9">
+        <v>0</v>
+      </c>
+      <c r="X78" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y78" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="AB78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE78" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AO78" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP78" s="4">
         <v>58</v>
       </c>
@@ -14164,7 +14918,7 @@
         <v>19698</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C91" s="4">
         <v>51</v>
@@ -14194,8 +14948,12 @@
         <v>58</v>
       </c>
       <c r="L91" s="4"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="6"/>
+      <c r="M91" s="5">
+        <v>0</v>
+      </c>
+      <c r="N91" s="6">
+        <v>0</v>
+      </c>
       <c r="O91" s="6"/>
       <c r="P91" s="7"/>
       <c r="Q91" s="8"/>
@@ -14573,7 +15331,7 @@
         <v>19706</v>
       </c>
       <c r="B94" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C94" s="4">
         <v>51</v>
@@ -14601,35 +15359,93 @@
         <v>58</v>
       </c>
       <c r="L94" s="4"/>
-      <c r="M94" s="5"/>
-      <c r="N94" s="6"/>
-      <c r="O94" s="6"/>
-      <c r="P94" s="7"/>
-      <c r="Q94" s="8"/>
-      <c r="R94" s="8"/>
-      <c r="S94" s="8"/>
-      <c r="T94" s="9"/>
-      <c r="U94" s="9"/>
-      <c r="V94" s="9"/>
-      <c r="W94" s="9"/>
-      <c r="X94" s="9"/>
-      <c r="Y94" s="9"/>
-      <c r="Z94" s="9"/>
-      <c r="AA94" s="9"/>
-      <c r="AB94" s="9"/>
-      <c r="AC94" s="9"/>
-      <c r="AD94" s="6"/>
-      <c r="AE94" s="6"/>
-      <c r="AF94" s="6"/>
-      <c r="AG94" s="6"/>
-      <c r="AH94" s="6"/>
-      <c r="AI94" s="6"/>
-      <c r="AJ94" s="6"/>
-      <c r="AK94" s="6"/>
-      <c r="AL94" s="6"/>
-      <c r="AM94" s="6"/>
-      <c r="AN94" s="9"/>
-      <c r="AO94" s="6"/>
+      <c r="M94" s="5">
+        <v>2322.8000000000002</v>
+      </c>
+      <c r="N94" s="6">
+        <v>27</v>
+      </c>
+      <c r="O94" s="6">
+        <v>16</v>
+      </c>
+      <c r="P94" s="7">
+        <v>9.8311099999999989</v>
+      </c>
+      <c r="Q94" s="8">
+        <v>28.653124999999999</v>
+      </c>
+      <c r="R94" s="8">
+        <v>10.413543750000001</v>
+      </c>
+      <c r="S94" s="8">
+        <v>8</v>
+      </c>
+      <c r="T94" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="U94" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V94" s="9">
+        <v>0</v>
+      </c>
+      <c r="W94" s="9">
+        <v>0</v>
+      </c>
+      <c r="X94" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE94" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP94" s="4">
         <v>58</v>
       </c>
@@ -18445,7 +19261,7 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="W121" s="9">
-        <v>0</v>
+        <v>0.066666666666000005</v>
       </c>
       <c r="X121" s="9">
         <v>0</v>
@@ -18475,7 +19291,7 @@
         <v>2</v>
       </c>
       <c r="AG121" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH121" s="6">
         <v>0</v>
@@ -20111,7 +20927,7 @@
         <v>19774</v>
       </c>
       <c r="B132" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C132" s="4">
         <v>51</v>
@@ -20141,35 +20957,93 @@
         <v>58</v>
       </c>
       <c r="L132" s="4"/>
-      <c r="M132" s="5"/>
-      <c r="N132" s="6"/>
-      <c r="O132" s="6"/>
-      <c r="P132" s="7"/>
-      <c r="Q132" s="8"/>
-      <c r="R132" s="8"/>
-      <c r="S132" s="8"/>
-      <c r="T132" s="9"/>
-      <c r="U132" s="9"/>
-      <c r="V132" s="9"/>
-      <c r="W132" s="9"/>
-      <c r="X132" s="9"/>
-      <c r="Y132" s="9"/>
-      <c r="Z132" s="9"/>
-      <c r="AA132" s="9"/>
-      <c r="AB132" s="9"/>
-      <c r="AC132" s="9"/>
-      <c r="AD132" s="6"/>
-      <c r="AE132" s="6"/>
-      <c r="AF132" s="6"/>
-      <c r="AG132" s="6"/>
-      <c r="AH132" s="6"/>
-      <c r="AI132" s="6"/>
-      <c r="AJ132" s="6"/>
-      <c r="AK132" s="6"/>
-      <c r="AL132" s="6"/>
-      <c r="AM132" s="6"/>
-      <c r="AN132" s="9"/>
-      <c r="AO132" s="6"/>
+      <c r="M132" s="5">
+        <v>6581.3199999999997</v>
+      </c>
+      <c r="N132" s="6">
+        <v>83</v>
+      </c>
+      <c r="O132" s="6">
+        <v>78</v>
+      </c>
+      <c r="P132" s="7">
+        <v>3.7845524390243903</v>
+      </c>
+      <c r="Q132" s="8">
+        <v>16.717948717948719</v>
+      </c>
+      <c r="R132" s="8">
+        <v>7.3928893333333328</v>
+      </c>
+      <c r="S132" s="8">
+        <v>6</v>
+      </c>
+      <c r="T132" s="9">
+        <v>0.55128205128205132</v>
+      </c>
+      <c r="U132" s="9">
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="V132" s="9">
+        <v>0</v>
+      </c>
+      <c r="W132" s="9">
+        <v>0</v>
+      </c>
+      <c r="X132" s="9">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="Y132" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="Z132" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="9">
+        <v>0.064102564102564097</v>
+      </c>
+      <c r="AB132" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC132" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="AD132" s="6">
+        <v>41</v>
+      </c>
+      <c r="AE132" s="6">
+        <v>34</v>
+      </c>
+      <c r="AF132" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG132" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI132" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ132" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK132" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL132" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM132" s="6">
+        <v>24</v>
+      </c>
+      <c r="AN132" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO132" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP132" s="4">
         <v>58</v>
       </c>
@@ -20742,7 +21616,7 @@
         <v>0</v>
       </c>
       <c r="W136" s="9">
-        <v>0</v>
+        <v>0.090909090908999998</v>
       </c>
       <c r="X136" s="9">
         <v>0</v>
@@ -20772,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="AG136" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH136" s="6">
         <v>0</v>
@@ -21148,7 +22022,7 @@
         <v>19790</v>
       </c>
       <c r="B139" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C139" s="4">
         <v>51</v>
@@ -21178,35 +22052,93 @@
         <v>58</v>
       </c>
       <c r="L139" s="4"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="6"/>
-      <c r="O139" s="6"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="8"/>
-      <c r="R139" s="8"/>
-      <c r="S139" s="8"/>
-      <c r="T139" s="9"/>
-      <c r="U139" s="9"/>
-      <c r="V139" s="9"/>
-      <c r="W139" s="9"/>
-      <c r="X139" s="9"/>
-      <c r="Y139" s="9"/>
-      <c r="Z139" s="9"/>
-      <c r="AA139" s="9"/>
-      <c r="AB139" s="9"/>
-      <c r="AC139" s="9"/>
-      <c r="AD139" s="6"/>
-      <c r="AE139" s="6"/>
-      <c r="AF139" s="6"/>
-      <c r="AG139" s="6"/>
-      <c r="AH139" s="6"/>
-      <c r="AI139" s="6"/>
-      <c r="AJ139" s="6"/>
-      <c r="AK139" s="6"/>
-      <c r="AL139" s="6"/>
-      <c r="AM139" s="6"/>
-      <c r="AN139" s="9"/>
-      <c r="AO139" s="6"/>
+      <c r="M139" s="5">
+        <v>5116.8299999999999</v>
+      </c>
+      <c r="N139" s="6">
+        <v>45</v>
+      </c>
+      <c r="O139" s="6">
+        <v>12</v>
+      </c>
+      <c r="P139" s="7">
+        <v>2.3075404761904763</v>
+      </c>
+      <c r="Q139" s="8">
+        <v>13.922224999999999</v>
+      </c>
+      <c r="R139" s="8">
+        <v>5.1515181818181821</v>
+      </c>
+      <c r="S139" s="8">
+        <v>7</v>
+      </c>
+      <c r="T139" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U139" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V139" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="W139" s="9">
+        <v>0.083333333332999998</v>
+      </c>
+      <c r="X139" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Z139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE139" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF139" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO139" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP139" s="4">
         <v>58</v>
       </c>
@@ -21755,7 +22687,7 @@
         <v>19798</v>
       </c>
       <c r="B144" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C144" s="4">
         <v>51</v>
@@ -21785,35 +22717,93 @@
         <v>58</v>
       </c>
       <c r="L144" s="4"/>
-      <c r="M144" s="5"/>
-      <c r="N144" s="6"/>
-      <c r="O144" s="6"/>
-      <c r="P144" s="7"/>
-      <c r="Q144" s="8"/>
-      <c r="R144" s="8"/>
-      <c r="S144" s="8"/>
-      <c r="T144" s="9"/>
-      <c r="U144" s="9"/>
-      <c r="V144" s="9"/>
-      <c r="W144" s="9"/>
-      <c r="X144" s="9"/>
-      <c r="Y144" s="9"/>
-      <c r="Z144" s="9"/>
-      <c r="AA144" s="9"/>
-      <c r="AB144" s="9"/>
-      <c r="AC144" s="9"/>
-      <c r="AD144" s="6"/>
-      <c r="AE144" s="6"/>
-      <c r="AF144" s="6"/>
-      <c r="AG144" s="6"/>
-      <c r="AH144" s="6"/>
-      <c r="AI144" s="6"/>
-      <c r="AJ144" s="6"/>
-      <c r="AK144" s="6"/>
-      <c r="AL144" s="6"/>
-      <c r="AM144" s="6"/>
-      <c r="AN144" s="9"/>
-      <c r="AO144" s="6"/>
+      <c r="M144" s="5">
+        <v>6460.2799999999997</v>
+      </c>
+      <c r="N144" s="6">
+        <v>84</v>
+      </c>
+      <c r="O144" s="6">
+        <v>56</v>
+      </c>
+      <c r="P144" s="7">
+        <v>2.8421686746987951</v>
+      </c>
+      <c r="Q144" s="8">
+        <v>14.220535714285715</v>
+      </c>
+      <c r="R144" s="8">
+        <v>5.1880509433962265</v>
+      </c>
+      <c r="S144" s="8">
+        <v>7</v>
+      </c>
+      <c r="T144" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="U144" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V144" s="9">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="W144" s="9">
+        <v>0</v>
+      </c>
+      <c r="X144" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Y144" s="9">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="Z144" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AB144" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AC144" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD144" s="6">
+        <v>22</v>
+      </c>
+      <c r="AE144" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF144" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG144" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH144" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI144" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ144" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK144" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL144" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM144" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN144" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO144" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP144" s="4">
         <v>58</v>
       </c>
@@ -22482,7 +23472,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>51</v>
@@ -22512,35 +23502,93 @@
         <v>58</v>
       </c>
       <c r="L149" s="4"/>
-      <c r="M149" s="5"/>
-      <c r="N149" s="6"/>
-      <c r="O149" s="6"/>
-      <c r="P149" s="7"/>
-      <c r="Q149" s="8"/>
-      <c r="R149" s="8"/>
-      <c r="S149" s="8"/>
-      <c r="T149" s="9"/>
-      <c r="U149" s="9"/>
-      <c r="V149" s="9"/>
-      <c r="W149" s="9"/>
-      <c r="X149" s="9"/>
-      <c r="Y149" s="9"/>
-      <c r="Z149" s="9"/>
-      <c r="AA149" s="9"/>
-      <c r="AB149" s="9"/>
-      <c r="AC149" s="9"/>
-      <c r="AD149" s="6"/>
-      <c r="AE149" s="6"/>
-      <c r="AF149" s="6"/>
-      <c r="AG149" s="6"/>
-      <c r="AH149" s="6"/>
-      <c r="AI149" s="6"/>
-      <c r="AJ149" s="6"/>
-      <c r="AK149" s="6"/>
-      <c r="AL149" s="6"/>
-      <c r="AM149" s="6"/>
-      <c r="AN149" s="9"/>
-      <c r="AO149" s="6"/>
+      <c r="M149" s="5">
+        <v>3369.5700000000002</v>
+      </c>
+      <c r="N149" s="6">
+        <v>38</v>
+      </c>
+      <c r="O149" s="6">
+        <v>28</v>
+      </c>
+      <c r="P149" s="7">
+        <v>8.3548236842105261</v>
+      </c>
+      <c r="Q149" s="8">
+        <v>42.507739285714287</v>
+      </c>
+      <c r="R149" s="8">
+        <v>28.70448846153846</v>
+      </c>
+      <c r="S149" s="8">
+        <v>7</v>
+      </c>
+      <c r="T149" s="9">
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="U149" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V149" s="9">
+        <v>0</v>
+      </c>
+      <c r="W149" s="9">
+        <v>0</v>
+      </c>
+      <c r="X149" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Y149" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Z149" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AB149" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD149" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE149" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH149" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI149" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK149" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM149" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN149" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO149" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP149" s="4">
         <v>58</v>
       </c>
@@ -23959,7 +25007,7 @@
         <v>19866</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>51</v>
@@ -23987,35 +25035,93 @@
         <v>58</v>
       </c>
       <c r="L160" s="4"/>
-      <c r="M160" s="5"/>
-      <c r="N160" s="6"/>
-      <c r="O160" s="6"/>
-      <c r="P160" s="7"/>
-      <c r="Q160" s="8"/>
-      <c r="R160" s="8"/>
-      <c r="S160" s="8"/>
-      <c r="T160" s="9"/>
-      <c r="U160" s="9"/>
-      <c r="V160" s="9"/>
-      <c r="W160" s="9"/>
-      <c r="X160" s="9"/>
-      <c r="Y160" s="9"/>
-      <c r="Z160" s="9"/>
-      <c r="AA160" s="9"/>
-      <c r="AB160" s="9"/>
-      <c r="AC160" s="9"/>
-      <c r="AD160" s="6"/>
-      <c r="AE160" s="6"/>
-      <c r="AF160" s="6"/>
-      <c r="AG160" s="6"/>
-      <c r="AH160" s="6"/>
-      <c r="AI160" s="6"/>
-      <c r="AJ160" s="6"/>
-      <c r="AK160" s="6"/>
-      <c r="AL160" s="6"/>
-      <c r="AM160" s="6"/>
-      <c r="AN160" s="9"/>
-      <c r="AO160" s="6"/>
+      <c r="M160" s="5">
+        <v>2649.73</v>
+      </c>
+      <c r="N160" s="6">
+        <v>29</v>
+      </c>
+      <c r="O160" s="6">
+        <v>23</v>
+      </c>
+      <c r="P160" s="7">
+        <v>5.1063206896551723</v>
+      </c>
+      <c r="Q160" s="8">
+        <v>19.755073913043478</v>
+      </c>
+      <c r="R160" s="8">
+        <v>7.4760869565217387</v>
+      </c>
+      <c r="S160" s="8">
+        <v>7</v>
+      </c>
+      <c r="T160" s="9">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="U160" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="V160" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="W160" s="9">
+        <v>0</v>
+      </c>
+      <c r="X160" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y160" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD160" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE160" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF160" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH160" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM160" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN160" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO160" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP160" s="4">
         <v>58</v>
       </c>
@@ -24054,7 +25160,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>51</v>
@@ -24084,35 +25190,91 @@
         <v>58</v>
       </c>
       <c r="L161" s="4"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="6"/>
-      <c r="O161" s="6"/>
-      <c r="P161" s="7"/>
-      <c r="Q161" s="8"/>
+      <c r="M161" s="5">
+        <v>3205.9000000000001</v>
+      </c>
+      <c r="N161" s="6">
+        <v>41</v>
+      </c>
+      <c r="O161" s="6">
+        <v>1</v>
+      </c>
+      <c r="P161" s="7">
+        <v>10.553507894736843</v>
+      </c>
+      <c r="Q161" s="8">
+        <v>1.9666999999999999</v>
+      </c>
       <c r="R161" s="8"/>
-      <c r="S161" s="8"/>
-      <c r="T161" s="9"/>
-      <c r="U161" s="9"/>
-      <c r="V161" s="9"/>
-      <c r="W161" s="9"/>
-      <c r="X161" s="9"/>
-      <c r="Y161" s="9"/>
-      <c r="Z161" s="9"/>
-      <c r="AA161" s="9"/>
-      <c r="AB161" s="9"/>
-      <c r="AC161" s="9"/>
-      <c r="AD161" s="6"/>
-      <c r="AE161" s="6"/>
-      <c r="AF161" s="6"/>
-      <c r="AG161" s="6"/>
-      <c r="AH161" s="6"/>
-      <c r="AI161" s="6"/>
-      <c r="AJ161" s="6"/>
-      <c r="AK161" s="6"/>
-      <c r="AL161" s="6"/>
-      <c r="AM161" s="6"/>
-      <c r="AN161" s="9"/>
-      <c r="AO161" s="6"/>
+      <c r="S161" s="8">
+        <v>5.2999999999999998</v>
+      </c>
+      <c r="T161" s="9">
+        <v>1</v>
+      </c>
+      <c r="U161" s="9">
+        <v>1</v>
+      </c>
+      <c r="V161" s="9">
+        <v>0</v>
+      </c>
+      <c r="W161" s="9">
+        <v>0</v>
+      </c>
+      <c r="X161" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y161" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB161" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO161" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP161" s="4">
         <v>58</v>
       </c>
@@ -24153,7 +25315,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24183,35 +25345,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>2874.8000000000002</v>
+      </c>
+      <c r="N162" s="6">
+        <v>31</v>
+      </c>
+      <c r="O162" s="6">
+        <v>13</v>
+      </c>
+      <c r="P162" s="7">
+        <v>3.1066666666666669</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>13.330769230769231</v>
+      </c>
+      <c r="R162" s="8">
+        <v>1.6205153846153846</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -26076,7 +27296,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -26106,35 +27326,93 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
-      <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="M175" s="5">
+        <v>2841.04</v>
+      </c>
+      <c r="N175" s="6">
+        <v>40</v>
+      </c>
+      <c r="O175" s="6">
+        <v>13</v>
+      </c>
+      <c r="P175" s="7">
+        <v>6.5529923076923078</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>17.971792307692308</v>
+      </c>
+      <c r="R175" s="8">
+        <v>4.532053846153846</v>
+      </c>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
+      <c r="T175" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="U175" s="9">
+        <v>0</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -26175,7 +27453,7 @@
         <v>19898</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C176" s="4">
         <v>51</v>
@@ -26203,35 +27481,93 @@
         <v>58</v>
       </c>
       <c r="L176" s="4"/>
-      <c r="M176" s="5"/>
-      <c r="N176" s="6"/>
-      <c r="O176" s="6"/>
-      <c r="P176" s="7"/>
-      <c r="Q176" s="8"/>
-      <c r="R176" s="8"/>
-      <c r="S176" s="8"/>
-      <c r="T176" s="9"/>
-      <c r="U176" s="9"/>
-      <c r="V176" s="9"/>
-      <c r="W176" s="9"/>
-      <c r="X176" s="9"/>
-      <c r="Y176" s="9"/>
-      <c r="Z176" s="9"/>
-      <c r="AA176" s="9"/>
-      <c r="AB176" s="9"/>
-      <c r="AC176" s="9"/>
-      <c r="AD176" s="6"/>
-      <c r="AE176" s="6"/>
-      <c r="AF176" s="6"/>
-      <c r="AG176" s="6"/>
-      <c r="AH176" s="6"/>
-      <c r="AI176" s="6"/>
-      <c r="AJ176" s="6"/>
-      <c r="AK176" s="6"/>
-      <c r="AL176" s="6"/>
-      <c r="AM176" s="6"/>
-      <c r="AN176" s="9"/>
-      <c r="AO176" s="6"/>
+      <c r="M176" s="5">
+        <v>1617.2</v>
+      </c>
+      <c r="N176" s="6">
+        <v>19</v>
+      </c>
+      <c r="O176" s="6">
+        <v>8</v>
+      </c>
+      <c r="P176" s="7">
+        <v>2.9714285714285715</v>
+      </c>
+      <c r="Q176" s="8">
+        <v>35.252087500000002</v>
+      </c>
+      <c r="R176" s="8">
+        <v>25.670837500000001</v>
+      </c>
+      <c r="S176" s="8">
+        <v>7</v>
+      </c>
+      <c r="T176" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="U176" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V176" s="9">
+        <v>0</v>
+      </c>
+      <c r="W176" s="9">
+        <v>0</v>
+      </c>
+      <c r="X176" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Y176" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD176" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE176" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH176" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO176" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP176" s="4">
         <v>58</v>
       </c>
@@ -26896,7 +28232,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -26926,35 +28262,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>2753.3000000000002</v>
+      </c>
+      <c r="N181" s="6">
+        <v>30</v>
+      </c>
+      <c r="O181" s="6">
+        <v>19</v>
+      </c>
+      <c r="P181" s="7">
+        <v>2.9977766666666668</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>10.529826315789473</v>
+      </c>
+      <c r="R181" s="8">
+        <v>0.43472500000000003</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>1</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27722,7 +29116,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27752,35 +29146,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1608.4000000000001</v>
+      </c>
+      <c r="N187" s="6">
+        <v>19</v>
+      </c>
+      <c r="O187" s="6">
+        <v>14</v>
+      </c>
+      <c r="P187" s="7">
+        <v>8.8964894736842108</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>27.973807142857144</v>
+      </c>
+      <c r="R187" s="8">
+        <v>11.613092857142858</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27978,7 +29430,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -28008,35 +29460,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>3580.2600000000002</v>
+      </c>
+      <c r="N189" s="6">
+        <v>51</v>
+      </c>
+      <c r="O189" s="6">
+        <v>46</v>
+      </c>
+      <c r="P189" s="7">
+        <v>4.0235849056603774</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>24.155797826086957</v>
+      </c>
+      <c r="R189" s="8">
+        <v>14.204925000000001</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.54347826086956519</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>29</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>25</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>23</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28077,7 +29587,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28107,35 +29617,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>2592.8200000000002</v>
+      </c>
+      <c r="N190" s="6">
+        <v>32</v>
+      </c>
+      <c r="O190" s="6">
+        <v>16</v>
+      </c>
+      <c r="P190" s="7">
+        <v>3.21875</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>16.71666875</v>
+      </c>
+      <c r="R190" s="8">
+        <v>6.06145625</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -29309,7 +30877,9 @@
       <c r="N198" s="6">
         <v>22</v>
       </c>
-      <c r="O198" s="6"/>
+      <c r="O198" s="6">
+        <v>14</v>
+      </c>
       <c r="P198" s="7">
         <v>9.1086956521739122</v>
       </c>
@@ -29319,31 +30889,75 @@
       <c r="R198" s="8">
         <v>4.3166666666666664</v>
       </c>
-      <c r="S198" s="8"/>
+      <c r="S198" s="8">
+        <v>7</v>
+      </c>
       <c r="T198" s="9">
         <v>0.14285714285714285</v>
       </c>
-      <c r="U198" s="9"/>
-      <c r="V198" s="9"/>
-      <c r="W198" s="9"/>
-      <c r="X198" s="9"/>
-      <c r="Y198" s="9"/>
-      <c r="Z198" s="9"/>
-      <c r="AA198" s="9"/>
-      <c r="AB198" s="9"/>
-      <c r="AC198" s="9"/>
-      <c r="AD198" s="6"/>
-      <c r="AE198" s="6"/>
-      <c r="AF198" s="6"/>
-      <c r="AG198" s="6"/>
-      <c r="AH198" s="6"/>
-      <c r="AI198" s="6"/>
-      <c r="AJ198" s="6"/>
-      <c r="AK198" s="6"/>
-      <c r="AL198" s="6"/>
-      <c r="AM198" s="6"/>
-      <c r="AN198" s="9"/>
-      <c r="AO198" s="6"/>
+      <c r="U198" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V198" s="9">
+        <v>0</v>
+      </c>
+      <c r="W198" s="9">
+        <v>0</v>
+      </c>
+      <c r="X198" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y198" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA198" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AB198" s="9">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="AC198" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD198" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE198" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ198" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK198" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL198" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM198" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN198" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO198" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP198" s="4">
         <v>58</v>
       </c>
@@ -29384,7 +30998,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -29414,35 +31028,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>2413.6999999999998</v>
+      </c>
+      <c r="N199" s="6">
+        <v>28</v>
+      </c>
+      <c r="O199" s="6">
+        <v>15</v>
+      </c>
+      <c r="P199" s="7">
+        <v>4.3752862068965523</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>15.564446666666667</v>
+      </c>
+      <c r="R199" s="8">
+        <v>5.5730769230769237</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -29483,7 +31155,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29513,35 +31185,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>1531.5899999999999</v>
+      </c>
+      <c r="N200" s="6">
+        <v>21</v>
+      </c>
+      <c r="O200" s="6">
+        <v>11</v>
+      </c>
+      <c r="P200" s="7">
+        <v>7.0848500000000003</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>23.727272727272727</v>
+      </c>
+      <c r="R200" s="8">
+        <v>8.0515181818181816</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 4.033,71</t>
-  </si>
-  <si>
-    <t>44.7</t>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 4.021,88</t>
+  </si>
+  <si>
+    <t>44.6</t>
   </si>
   <si>
     <t>28.3</t>
   </si>
   <si>
-    <t>4.74</t>
+    <t>4.75</t>
   </si>
   <si>
     <t>18.4</t>
@@ -962,7 +962,7 @@
     <t>44.3%</t>
   </si>
   <si>
-    <t>19.0%</t>
+    <t>18.9%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -989,10 +989,10 @@
     <t>4.0%</t>
   </si>
   <si>
-    <t>1244.0</t>
-  </si>
-  <si>
-    <t>974.0</t>
+    <t>1246.0</t>
+  </si>
+  <si>
+    <t>975.0</t>
   </si>
   <si>
     <t>120.0</t>
@@ -1001,7 +1001,7 @@
     <t>12.0</t>
   </si>
   <si>
-    <t>277.0</t>
+    <t>278.0</t>
   </si>
   <si>
     <t>83.0</t>
@@ -1010,7 +1010,7 @@
     <t>16.0</t>
   </si>
   <si>
-    <t>366.0</t>
+    <t>367.0</t>
   </si>
   <si>
     <t>140.0</t>
@@ -16523,7 +16523,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16553,35 +16553,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>1892.74</v>
+      </c>
+      <c r="N102" s="6">
+        <v>22</v>
+      </c>
+      <c r="O102" s="6">
+        <v>18</v>
+      </c>
+      <c r="P102" s="7">
+        <v>5.5106045454545454</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>19.387038888888888</v>
+      </c>
+      <c r="R102" s="8">
+        <v>7.0601833333333328</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
@@ -932,37 +932,40 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 4.021,88</t>
-  </si>
-  <si>
-    <t>44.6</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>4.75</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 4.035,57</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>4.76</t>
   </si>
   <si>
     <t>18.4</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>44.3%</t>
-  </si>
-  <si>
-    <t>18.9%</t>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>44.0%</t>
+  </si>
+  <si>
+    <t>19.1%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -980,49 +983,49 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>7.1%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
+    <t>7.2%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
   </si>
   <si>
     <t>4.0%</t>
   </si>
   <si>
-    <t>1246.0</t>
-  </si>
-  <si>
-    <t>975.0</t>
-  </si>
-  <si>
-    <t>120.0</t>
+    <t>1290.0</t>
+  </si>
+  <si>
+    <t>1011.0</t>
+  </si>
+  <si>
+    <t>122.0</t>
   </si>
   <si>
     <t>12.0</t>
   </si>
   <si>
-    <t>278.0</t>
-  </si>
-  <si>
-    <t>83.0</t>
+    <t>286.0</t>
+  </si>
+  <si>
+    <t>84.0</t>
   </si>
   <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>367.0</t>
-  </si>
-  <si>
-    <t>140.0</t>
-  </si>
-  <si>
-    <t>205.0</t>
+    <t>384.0</t>
+  </si>
+  <si>
+    <t>146.0</t>
+  </si>
+  <si>
+    <t>213.0</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>37.0</t>
+    <t>39.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6529,7 +6532,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6559,35 +6562,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>8711.0900000000001</v>
+      </c>
+      <c r="N34" s="6">
+        <v>86</v>
+      </c>
+      <c r="O34" s="6">
+        <v>53</v>
+      </c>
+      <c r="P34" s="7">
+        <v>9.91144578313253</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>17.119811320754717</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.2846938775510206</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.47169811320754718</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.35849056603773582</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.22641509433962265</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.11320754716981132</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -12803,7 +12864,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12831,35 +12892,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>4251.7700000000004</v>
+      </c>
+      <c r="N76" s="6">
+        <v>53</v>
+      </c>
+      <c r="O76" s="6">
+        <v>29</v>
+      </c>
+      <c r="P76" s="7">
+        <v>2.6326803921568627</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>16.643679310344826</v>
+      </c>
+      <c r="R76" s="8">
+        <v>5.4716037037037042</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -18569,33 +18688,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>19</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22336,7 +22501,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22366,35 +22531,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>1621.5799999999999</v>
+      </c>
+      <c r="N141" s="6">
+        <v>26</v>
+      </c>
+      <c r="O141" s="6">
+        <v>12</v>
+      </c>
+      <c r="P141" s="7">
+        <v>3.7007260869565215</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>13.573608333333333</v>
+      </c>
+      <c r="R141" s="8">
+        <v>2.1555583333333335</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33255,137 +33478,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>41</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Z217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AA217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>336</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>337</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>338</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>338</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>339</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>339</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 4.035,57</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 4.034,60</t>
   </si>
   <si>
     <t>44.7</t>
@@ -950,10 +950,10 @@
     <t>28.4</t>
   </si>
   <si>
-    <t>4.76</t>
-  </si>
-  <si>
-    <t>18.4</t>
+    <t>4.75</t>
+  </si>
+  <si>
+    <t>18.3</t>
   </si>
   <si>
     <t>6.9</t>
@@ -962,7 +962,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>44.0%</t>
+    <t>44.3%</t>
   </si>
   <si>
     <t>19.1%</t>
@@ -25145,7 +25145,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25175,18 +25175,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>3855.3600000000001</v>
+      </c>
+      <c r="N159" s="6">
+        <v>49</v>
+      </c>
       <c r="O159" s="6">
         <v>32</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>3.8710877551020411</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>14.609896875</v>
+      </c>
+      <c r="R159" s="8">
+        <v>4.4040241379310343</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.5625</v>
+      </c>
       <c r="U159" s="9">
         <v>0.1875</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
@@ -938,22 +938,22 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 4.034,60</t>
-  </si>
-  <si>
-    <t>44.7</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 4.030,58</t>
+  </si>
+  <si>
+    <t>44.6</t>
   </si>
   <si>
     <t>28.4</t>
   </si>
   <si>
-    <t>4.75</t>
-  </si>
-  <si>
-    <t>18.3</t>
+    <t>4.76</t>
+  </si>
+  <si>
+    <t>18.4</t>
   </si>
   <si>
     <t>6.9</t>
@@ -962,7 +962,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>44.3%</t>
+    <t>44.4%</t>
   </si>
   <si>
     <t>19.1%</t>
@@ -14837,7 +14837,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14865,14 +14865,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>3286.52</v>
+      </c>
+      <c r="N89" s="6">
+        <v>27</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>5.2858037037037038</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>19.796666666666667</v>
+      </c>
+      <c r="R89" s="8">
+        <v>5.4955533333333335</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29153,7 +29165,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31861,7 +31873,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33494,7 +33506,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-07).xlsx
@@ -938,43 +938,43 @@
     <t>215</t>
   </si>
   <si>
-    <t>27</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.030,58</t>
+    <t>R$ 3.978,77</t>
   </si>
   <si>
-    <t>44.6</t>
+    <t>44.1</t>
   </si>
   <si>
-    <t>28.4</t>
+    <t>28.3</t>
   </si>
   <si>
-    <t>4.76</t>
+    <t>4.74</t>
   </si>
   <si>
-    <t>18.4</t>
+    <t>18.3</t>
   </si>
   <si>
     <t>6.9</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>44.4%</t>
+    <t>44.3%</t>
   </si>
   <si>
-    <t>19.1%</t>
+    <t>18.8%</t>
   </si>
   <si>
-    <t>2.3%</t>
+    <t>2.2%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.4%</t>
+    <t>5.3%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -983,43 +983,43 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>7.2%</t>
+    <t>7.1%</t>
   </si>
   <si>
-    <t>2.8%</t>
+    <t>2.7%</t>
   </si>
   <si>
     <t>4.0%</t>
   </si>
   <si>
-    <t>1290.0</t>
+    <t>1300.0</t>
   </si>
   <si>
-    <t>1011.0</t>
+    <t>1019.0</t>
   </si>
   <si>
     <t>122.0</t>
   </si>
   <si>
-    <t>12.0</t>
+    <t>13.0</t>
   </si>
   <si>
-    <t>286.0</t>
+    <t>287.0</t>
   </si>
   <si>
-    <t>84.0</t>
+    <t>85.0</t>
   </si>
   <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>384.0</t>
+    <t>388.0</t>
   </si>
   <si>
-    <t>146.0</t>
+    <t>148.0</t>
   </si>
   <si>
-    <t>213.0</t>
+    <t>215.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -9193,7 +9193,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9223,14 +9223,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>498.10000000000002</v>
+      </c>
+      <c r="N51" s="6">
+        <v>7</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>1.4785714285714284</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>20.794433333333334</v>
+      </c>
+      <c r="R51" s="8">
+        <v>11.75</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10262,33 +10274,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>41</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.024390243902000001</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24077,7 +24135,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24107,35 +24165,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2740.8400000000001</v>
+      </c>
+      <c r="N151" s="6">
+        <v>32</v>
+      </c>
+      <c r="O151" s="6">
+        <v>30</v>
+      </c>
+      <c r="P151" s="7">
+        <v>4.0125000000000002</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>13.386666666666667</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.3144433333333336</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24959,7 +25075,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -24989,35 +25105,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>1924.5999999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>20</v>
+      </c>
+      <c r="O157" s="6">
+        <v>15</v>
+      </c>
+      <c r="P157" s="7">
+        <v>5.8008350000000002</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>16.568886666666668</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.8133333333333335</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25058,7 +25232,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25088,35 +25262,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2117.8400000000001</v>
+      </c>
+      <c r="N158" s="6">
+        <v>22</v>
+      </c>
+      <c r="O158" s="6">
+        <v>18</v>
+      </c>
+      <c r="P158" s="7">
+        <v>4.4127000000000001</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>15.058333333333334</v>
+      </c>
+      <c r="R158" s="8">
+        <v>3.8620388888888888</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26091,7 +26323,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26121,35 +26353,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>2976.2800000000002</v>
+      </c>
+      <c r="N165" s="6">
+        <v>31</v>
+      </c>
+      <c r="O165" s="6">
+        <v>23</v>
+      </c>
+      <c r="P165" s="7">
+        <v>4.402776666666667</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>13.254347826086958</v>
+      </c>
+      <c r="R165" s="8">
+        <v>2.2287863636363636</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
